--- a/年报存档/入表财务效应分析样本.xlsx
+++ b/年报存档/入表财务效应分析样本.xlsx
@@ -6657,15 +6657,12 @@
         <v>13968410639.05</v>
       </c>
       <c r="K63" t="n">
-        <v>134227635.38</v>
+        <v>126399323.66</v>
       </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>净利润</t>
         </is>
-      </c>
-      <c r="M63" t="n">
-        <v>268794606.38</v>
       </c>
       <c r="N63" t="n">
         <v>33529751.5</v>
@@ -6691,19 +6688,19 @@
         <v>0.1119999763220026</v>
       </c>
       <c r="V63" t="n">
-        <v>0.9609370661308745</v>
+        <v>0.9048940994520798</v>
       </c>
       <c r="W63" t="n">
         <v>0.2245552583649794</v>
       </c>
       <c r="X63" t="n">
-        <v>102860834.78</v>
+        <v>95032523.06</v>
       </c>
       <c r="Y63" t="n">
-        <v>0.7363818077658951</v>
+        <v>0.6803388410871004</v>
       </c>
       <c r="Z63" t="n">
-        <v>23.36836264097198</v>
+        <v>24.81563958710189</v>
       </c>
       <c r="AA63" t="n">
         <v>0</v>
@@ -6713,7 +6710,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>报表金额与项目名上下错位一行（p143-153）。总资产、归母净利润取主要会计数据（p9，上期为调整后数）；净利润按错位还原（=归母 33,529,751.50 + 少数股东 100,697,883.88）；研发费用无法确定，置空</t>
+          <t>报表金额与项目名上下错位一行（p143-153）。总资产、归母净利润取主要会计数据（p9，上期为调整后数）；净利润取 CSMAR 利润表；上年净利润经追溯调整、无法确定，置空；研发费用无法确定，置空</t>
         </is>
       </c>
     </row>
@@ -8185,12 +8182,15 @@
         <v>771944258710</v>
       </c>
       <c r="K79" t="n">
-        <v>23384093178</v>
+        <v>30346608238</v>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>归母净利润</t>
-        </is>
+          <t>净利润</t>
+        </is>
+      </c>
+      <c r="M79" t="n">
+        <v>30236162855</v>
       </c>
       <c r="N79" t="n">
         <v>23384093178</v>
@@ -8216,19 +8216,19 @@
         <v>0.0003608930157435299</v>
       </c>
       <c r="V79" t="n">
-        <v>3.029246336656131</v>
+        <v>3.93119164960335</v>
       </c>
       <c r="W79" t="n">
         <v>0.0008687642824375764</v>
       </c>
       <c r="X79" t="n">
-        <v>23377386802</v>
+        <v>30339901862</v>
       </c>
       <c r="Y79" t="n">
-        <v>3.028377572373693</v>
+        <v>3.930322885320912</v>
       </c>
       <c r="Z79" t="n">
-        <v>0.02867922202050336</v>
+        <v>0.02209926047551595</v>
       </c>
       <c r="AA79" t="n">
         <v>0</v>
@@ -8238,7 +8238,7 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>程序误取追溯调整表（p219），作废。总资产、营业收入、归母净利润取主要会计数据（p13，上期为调整后数）；净利润置空</t>
+          <t>程序误取追溯调整表（p219），作废。总资产、营业收入、归母净利润取主要会计数据（p13，上期为调整后数）；净利润取 CSMAR 利润表，上年净利润取 p219 追溯调整表的调整后数</t>
         </is>
       </c>
     </row>
@@ -14196,12 +14196,15 @@
         <v>5984624114.13</v>
       </c>
       <c r="K142" t="n">
-        <v>1753652721</v>
+        <v>1812955974.25</v>
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>归母净利润</t>
-        </is>
+          <t>净利润</t>
+        </is>
+      </c>
+      <c r="M142" t="n">
+        <v>1428086862.83</v>
       </c>
       <c r="N142" t="n">
         <v>1753652721</v>
@@ -14221,19 +14224,19 @@
         <v>0.001666463735972457</v>
       </c>
       <c r="V142" t="n">
-        <v>29.30263768545692</v>
+        <v>30.29356463624038</v>
       </c>
       <c r="W142" t="n">
         <v>0.03387734904207485</v>
       </c>
       <c r="X142" t="n">
-        <v>1751625289</v>
+        <v>1810928542.25</v>
       </c>
       <c r="Y142" t="n">
-        <v>29.26876033641485</v>
+        <v>30.25968728719831</v>
       </c>
       <c r="Z142" t="n">
-        <v>0.1156119438998093</v>
+        <v>0.1118301838983556</v>
       </c>
       <c r="AA142" t="n">
         <v>0</v>
@@ -14243,7 +14246,7 @@
       </c>
       <c r="AC142" t="inlineStr">
         <is>
-          <t>财务报表页无文字层，程序未找到报表；取主要会计数据（p20）；净利润置空</t>
+          <t>财务报表页无文字层，程序未找到报表；总资产、营业收入、归母净利润取主要会计数据（p20），净利润取 CSMAR 利润表</t>
         </is>
       </c>
     </row>
@@ -20941,12 +20944,15 @@
         <v>731108751343</v>
       </c>
       <c r="K213" t="n">
-        <v>14751374779</v>
+        <v>20804131324</v>
       </c>
       <c r="L213" t="inlineStr">
         <is>
-          <t>归母净利润</t>
-        </is>
+          <t>净利润</t>
+        </is>
+      </c>
+      <c r="M213" t="n">
+        <v>30346608238</v>
       </c>
       <c r="N213" t="n">
         <v>14751374779</v>
@@ -20972,19 +20978,19 @@
         <v>0.001113945813837258</v>
       </c>
       <c r="V213" t="n">
-        <v>2.01767175565915</v>
+        <v>2.845559061601183</v>
       </c>
       <c r="W213" t="n">
         <v>0.003076427817159017</v>
       </c>
       <c r="X213" t="n">
-        <v>14728882746</v>
+        <v>20781639291</v>
       </c>
       <c r="Y213" t="n">
-        <v>2.014595327841991</v>
+        <v>2.842482633784024</v>
       </c>
       <c r="Z213" t="n">
-        <v>0.152474147914807</v>
+        <v>0.1081133004291932</v>
       </c>
       <c r="AA213" t="n">
         <v>0</v>
@@ -20994,7 +21000,7 @@
       </c>
       <c r="AC213" t="inlineStr">
         <is>
-          <t>财务报表页无文字层，程序未找到报表；取主要会计数据（p14）；净利润置空</t>
+          <t>财务报表页无文字层，程序未找到报表；总资产、营业收入、归母净利润取主要会计数据（p14），净利润取 CSMAR 利润表</t>
         </is>
       </c>
     </row>
@@ -23305,7 +23311,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G80"/>
+  <dimension ref="A1:G84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23731,7 +23737,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>报表金额与项目名上下错位一行（p143-153）。总资产、归母净利润取主要会计数据（p9，上期为调整后数）；净利润按错位还原（=归母 33,529,751.50 + 少数股东 100,697,883.88）；研发费用无法确定，置空</t>
+          <t>报表金额与项目名上下错位一行（p143-153）。总资产、归母净利润取主要会计数据（p9，上期为调整后数）；净利润取 CSMAR 利润表；上年净利润经追溯调整、无法确定，置空；研发费用无法确定，置空</t>
         </is>
       </c>
     </row>
@@ -23761,7 +23767,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>报表金额与项目名上下错位一行（p143-153）。总资产、归母净利润取主要会计数据（p9，上期为调整后数）；净利润按错位还原（=归母 33,529,751.50 + 少数股东 100,697,883.88）；研发费用无法确定，置空</t>
+          <t>报表金额与项目名上下错位一行（p143-153）。总资产、归母净利润取主要会计数据（p9，上期为调整后数）；净利润取 CSMAR 利润表；上年净利润经追溯调整、无法确定，置空；研发费用无法确定，置空</t>
         </is>
       </c>
     </row>
@@ -23787,11 +23793,11 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>134227635.38</v>
+        <v>126399323.66</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>报表金额与项目名上下错位一行（p143-153）。总资产、归母净利润取主要会计数据（p9，上期为调整后数）；净利润按错位还原（=归母 33,529,751.50 + 少数股东 100,697,883.88）；研发费用无法确定，置空</t>
+          <t>报表金额与项目名上下错位一行（p143-153）。总资产、归母净利润取主要会计数据（p9，上期为调整后数）；净利润取 CSMAR 利润表；上年净利润经追溯调整、无法确定，置空；研发费用无法确定，置空</t>
         </is>
       </c>
     </row>
@@ -23816,12 +23822,9 @@
           <t>ni0</t>
         </is>
       </c>
-      <c r="F17" t="n">
-        <v>268794606.38</v>
-      </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>报表金额与项目名上下错位一行（p143-153）。总资产、归母净利润取主要会计数据（p9，上期为调整后数）；净利润按错位还原（=归母 33,529,751.50 + 少数股东 100,697,883.88）；研发费用无法确定，置空</t>
+          <t>报表金额与项目名上下错位一行（p143-153）。总资产、归母净利润取主要会计数据（p9，上期为调整后数）；净利润取 CSMAR 利润表；上年净利润经追溯调整、无法确定，置空；研发费用无法确定，置空</t>
         </is>
       </c>
     </row>
@@ -23851,7 +23854,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>报表金额与项目名上下错位一行（p143-153）。总资产、归母净利润取主要会计数据（p9，上期为调整后数）；净利润按错位还原（=归母 33,529,751.50 + 少数股东 100,697,883.88）；研发费用无法确定，置空</t>
+          <t>报表金额与项目名上下错位一行（p143-153）。总资产、归母净利润取主要会计数据（p9，上期为调整后数）；净利润取 CSMAR 利润表；上年净利润经追溯调整、无法确定，置空；研发费用无法确定，置空</t>
         </is>
       </c>
     </row>
@@ -23881,7 +23884,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>报表金额与项目名上下错位一行（p143-153）。总资产、归母净利润取主要会计数据（p9，上期为调整后数）；净利润按错位还原（=归母 33,529,751.50 + 少数股东 100,697,883.88）；研发费用无法确定，置空</t>
+          <t>报表金额与项目名上下错位一行（p143-153）。总资产、归母净利润取主要会计数据（p9，上期为调整后数）；净利润取 CSMAR 利润表；上年净利润经追溯调整、无法确定，置空；研发费用无法确定，置空</t>
         </is>
       </c>
     </row>
@@ -23911,7 +23914,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>报表金额与项目名上下错位一行（p143-153）。总资产、归母净利润取主要会计数据（p9，上期为调整后数）；净利润按错位还原（=归母 33,529,751.50 + 少数股东 100,697,883.88）；研发费用无法确定，置空</t>
+          <t>报表金额与项目名上下错位一行（p143-153）。总资产、归母净利润取主要会计数据（p9，上期为调整后数）；净利润取 CSMAR 利润表；上年净利润经追溯调整、无法确定，置空；研发费用无法确定，置空</t>
         </is>
       </c>
     </row>
@@ -24184,7 +24187,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>程序误取追溯调整表（p219），作废。总资产、营业收入、归母净利润取主要会计数据（p13，上期为调整后数）；净利润置空</t>
+          <t>程序误取追溯调整表（p219），作废。总资产、营业收入、归母净利润取主要会计数据（p13，上期为调整后数）；净利润取 CSMAR 利润表，上年净利润取 p219 追溯调整表的调整后数</t>
         </is>
       </c>
     </row>
@@ -24217,7 +24220,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>程序误取追溯调整表（p219），作废。总资产、营业收入、归母净利润取主要会计数据（p13，上期为调整后数）；净利润置空</t>
+          <t>程序误取追溯调整表（p219），作废。总资产、营业收入、归母净利润取主要会计数据（p13，上期为调整后数）；净利润取 CSMAR 利润表，上年净利润取 p219 追溯调整表的调整后数</t>
         </is>
       </c>
     </row>
@@ -24247,7 +24250,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>程序误取追溯调整表（p219），作废。总资产、营业收入、归母净利润取主要会计数据（p13，上期为调整后数）；净利润置空</t>
+          <t>程序误取追溯调整表（p219），作废。总资产、营业收入、归母净利润取主要会计数据（p13，上期为调整后数）；净利润取 CSMAR 利润表，上年净利润取 p219 追溯调整表的调整后数</t>
         </is>
       </c>
     </row>
@@ -24277,7 +24280,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>程序误取追溯调整表（p219），作废。总资产、营业收入、归母净利润取主要会计数据（p13，上期为调整后数）；净利润置空</t>
+          <t>程序误取追溯调整表（p219），作废。总资产、营业收入、归母净利润取主要会计数据（p13，上期为调整后数）；净利润取 CSMAR 利润表，上年净利润取 p219 追溯调整表的调整后数</t>
         </is>
       </c>
     </row>
@@ -24305,9 +24308,12 @@
       <c r="E33" t="n">
         <v>30224114836</v>
       </c>
+      <c r="F33" t="n">
+        <v>30346608238</v>
+      </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>程序误取追溯调整表（p219），作废。总资产、营业收入、归母净利润取主要会计数据（p13，上期为调整后数）；净利润置空</t>
+          <t>程序误取追溯调整表（p219），作废。总资产、营业收入、归母净利润取主要会计数据（p13，上期为调整后数）；净利润取 CSMAR 利润表，上年净利润取 p219 追溯调整表的调整后数</t>
         </is>
       </c>
     </row>
@@ -24335,9 +24341,12 @@
       <c r="E34" t="n">
         <v>12048019</v>
       </c>
+      <c r="F34" t="n">
+        <v>30236162855</v>
+      </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>程序误取追溯调整表（p219），作废。总资产、营业收入、归母净利润取主要会计数据（p13，上期为调整后数）；净利润置空</t>
+          <t>程序误取追溯调整表（p219），作废。总资产、营业收入、归母净利润取主要会计数据（p13，上期为调整后数）；净利润取 CSMAR 利润表，上年净利润取 p219 追溯调整表的调整后数</t>
         </is>
       </c>
     </row>
@@ -24367,7 +24376,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>程序误取追溯调整表（p219），作废。总资产、营业收入、归母净利润取主要会计数据（p13，上期为调整后数）；净利润置空</t>
+          <t>程序误取追溯调整表（p219），作废。总资产、营业收入、归母净利润取主要会计数据（p13，上期为调整后数）；净利润取 CSMAR 利润表，上年净利润取 p219 追溯调整表的调整后数</t>
         </is>
       </c>
     </row>
@@ -24397,7 +24406,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>程序误取追溯调整表（p219），作废。总资产、营业收入、归母净利润取主要会计数据（p13，上期为调整后数）；净利润置空</t>
+          <t>程序误取追溯调整表（p219），作废。总资产、营业收入、归母净利润取主要会计数据（p13，上期为调整后数）；净利润取 CSMAR 利润表，上年净利润取 p219 追溯调整表的调整后数</t>
         </is>
       </c>
     </row>
@@ -24910,7 +24919,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>财务报表页无文字层，程序未找到报表；取主要会计数据（p20）；净利润置空</t>
+          <t>财务报表页无文字层，程序未找到报表；总资产、营业收入、归母净利润取主要会计数据（p20），净利润取 CSMAR 利润表</t>
         </is>
       </c>
     </row>
@@ -24940,7 +24949,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>财务报表页无文字层，程序未找到报表；取主要会计数据（p20）；净利润置空</t>
+          <t>财务报表页无文字层，程序未找到报表；总资产、营业收入、归母净利润取主要会计数据（p20），净利润取 CSMAR 利润表</t>
         </is>
       </c>
     </row>
@@ -24970,7 +24979,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>财务报表页无文字层，程序未找到报表；取主要会计数据（p20）；净利润置空</t>
+          <t>财务报表页无文字层，程序未找到报表；总资产、营业收入、归母净利润取主要会计数据（p20），净利润取 CSMAR 利润表</t>
         </is>
       </c>
     </row>
@@ -25000,7 +25009,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>财务报表页无文字层，程序未找到报表；取主要会计数据（p20）；净利润置空</t>
+          <t>财务报表页无文字层，程序未找到报表；总资产、营业收入、归母净利润取主要会计数据（p20），净利润取 CSMAR 利润表</t>
         </is>
       </c>
     </row>
@@ -25022,15 +25031,15 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>np</t>
+          <t>ni</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>1753652721</v>
+        <v>1812955974.25</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>财务报表页无文字层，程序未找到报表；取主要会计数据（p20）；净利润置空</t>
+          <t>财务报表页无文字层，程序未找到报表；总资产、营业收入、归母净利润取主要会计数据（p20），净利润取 CSMAR 利润表</t>
         </is>
       </c>
     </row>
@@ -25052,15 +25061,15 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>np0</t>
+          <t>ni0</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>1403260839.02</v>
+        <v>1428086862.83</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>财务报表页无文字层，程序未找到报表；取主要会计数据（p20）；净利润置空</t>
+          <t>财务报表页无文字层，程序未找到报表；总资产、营业收入、归母净利润取主要会计数据（p20），净利润取 CSMAR 利润表</t>
         </is>
       </c>
     </row>
@@ -25072,12 +25081,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>600029</t>
+          <t>002673</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>南方航空</t>
+          <t>西部证券</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -25086,11 +25095,11 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>857000000</v>
+        <v>1753652721</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>项目名为「归属于母公司股东的净利润/(亏损)」（p98）；按原文补录</t>
+          <t>财务报表页无文字层，程序未找到报表；总资产、营业收入、归母净利润取主要会计数据（p20），净利润取 CSMAR 利润表</t>
         </is>
       </c>
     </row>
@@ -25102,12 +25111,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>600029</t>
+          <t>002673</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>南方航空</t>
+          <t>西部证券</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -25116,11 +25125,11 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>-1696000000</v>
+        <v>1403260839.02</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>项目名为「归属于母公司股东的净利润/(亏损)」（p98）；按原文补录</t>
+          <t>财务报表页无文字层，程序未找到报表；总资产、营业收入、归母净利润取主要会计数据（p20），净利润取 CSMAR 利润表</t>
         </is>
       </c>
     </row>
@@ -25132,12 +25141,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>600030</t>
+          <t>600029</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>中信证券</t>
+          <t>南方航空</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -25146,11 +25155,11 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>30076100951.5</v>
+        <v>857000000</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>归母净利润行项目名折行（p183）；按原文补录</t>
+          <t>项目名为「归属于母公司股东的净利润/(亏损)」（p98）；按原文补录</t>
         </is>
       </c>
     </row>
@@ -25162,12 +25171,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>600030</t>
+          <t>600029</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>中信证券</t>
+          <t>南方航空</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -25176,11 +25185,11 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>21703696593.02</v>
+        <v>-1696000000</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>归母净利润行项目名折行（p183）；按原文补录</t>
+          <t>项目名为「归属于母公司股东的净利润/(亏损)」（p98）；按原文补录</t>
         </is>
       </c>
     </row>
@@ -25192,25 +25201,25 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>600050</t>
+          <t>600030</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>中国联通</t>
+          <t>中信证券</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>rev</t>
+          <t>np</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>392222880560</v>
+        <v>30076100951.5</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>同 2024 年；取主要会计数据（p7）</t>
+          <t>归母净利润行项目名折行（p183）；按原文补录</t>
         </is>
       </c>
     </row>
@@ -25222,25 +25231,25 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>600050</t>
+          <t>600030</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>中国联通</t>
+          <t>中信证券</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>rev0</t>
+          <t>np0</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>389589219642</v>
+        <v>21703696593.02</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>同 2024 年；取主要会计数据（p7）</t>
+          <t>归母净利润行项目名折行（p183）；按原文补录</t>
         </is>
       </c>
     </row>
@@ -25252,12 +25261,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>600600</t>
+          <t>600050</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>青岛啤酒</t>
+          <t>中国联通</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -25266,11 +25275,11 @@
         </is>
       </c>
       <c r="F65" t="n">
-        <v>32473493664</v>
+        <v>392222880560</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>利润表营业收入行未识别（p72）；取主要会计数据（p5）</t>
+          <t>同 2024 年；取主要会计数据（p7）</t>
         </is>
       </c>
     </row>
@@ -25282,12 +25291,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>600600</t>
+          <t>600050</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>青岛啤酒</t>
+          <t>中国联通</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -25296,11 +25305,11 @@
         </is>
       </c>
       <c r="F66" t="n">
-        <v>32137830111</v>
+        <v>389589219642</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>利润表营业收入行未识别（p72）；取主要会计数据（p5）</t>
+          <t>同 2024 年；取主要会计数据（p7）</t>
         </is>
       </c>
     </row>
@@ -25312,25 +25321,25 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>600926</t>
+          <t>600600</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>杭州银行</t>
+          <t>青岛啤酒</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>np</t>
+          <t>rev</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>19029250000</v>
+        <v>32473493664</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>归母净利润行项目名折行（p118）；按原文补录</t>
+          <t>利润表营业收入行未识别（p72）；取主要会计数据（p5）</t>
         </is>
       </c>
     </row>
@@ -25342,25 +25351,25 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>600926</t>
+          <t>600600</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>杭州银行</t>
+          <t>青岛啤酒</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>np0</t>
+          <t>rev0</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>16982563000</v>
+        <v>32137830111</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>归母净利润行项目名折行（p118）；按原文补录</t>
+          <t>利润表营业收入行未识别（p72）；取主要会计数据（p5）</t>
         </is>
       </c>
     </row>
@@ -25372,12 +25381,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>601066</t>
+          <t>600926</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>中信建投</t>
+          <t>杭州银行</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -25386,11 +25395,11 @@
         </is>
       </c>
       <c r="F69" t="n">
-        <v>9439423821.459999</v>
+        <v>19029250000</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>项目名前有「-」号（p170）；按原文补录</t>
+          <t>归母净利润行项目名折行（p118）；按原文补录</t>
         </is>
       </c>
     </row>
@@ -25402,12 +25411,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>601066</t>
+          <t>600926</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>中信建投</t>
+          <t>杭州银行</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -25416,11 +25425,11 @@
         </is>
       </c>
       <c r="F70" t="n">
-        <v>7223221368.58</v>
+        <v>16982563000</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>项目名前有「-」号（p170）；按原文补录</t>
+          <t>归母净利润行项目名折行（p118）；按原文补录</t>
         </is>
       </c>
     </row>
@@ -25432,12 +25441,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>601066</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>渝农商行</t>
+          <t>中信建投</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -25446,11 +25455,11 @@
         </is>
       </c>
       <c r="F71" t="n">
-        <v>12128421000</v>
+        <v>9439423821.459999</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>归母净利润行项目名折行（p199）；按原文补录</t>
+          <t>项目名前有「-」号（p170）；按原文补录</t>
         </is>
       </c>
     </row>
@@ -25462,12 +25471,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>601066</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>渝农商行</t>
+          <t>中信建投</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -25476,11 +25485,11 @@
         </is>
       </c>
       <c r="F72" t="n">
-        <v>11512747000</v>
+        <v>7223221368.58</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>归母净利润行项目名折行（p199）；按原文补录</t>
+          <t>项目名前有「-」号（p170）；按原文补录</t>
         </is>
       </c>
     </row>
@@ -25492,25 +25501,25 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>601728</t>
+          <t>601077</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>中国电信</t>
+          <t>渝农商行</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>rev</t>
+          <t>np</t>
         </is>
       </c>
       <c r="F73" t="n">
-        <v>523924731368.75</v>
+        <v>12128421000</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>同 2024 年；取主要会计数据（p7）</t>
+          <t>归母净利润行项目名折行（p199）；按原文补录</t>
         </is>
       </c>
     </row>
@@ -25522,25 +25531,25 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>601728</t>
+          <t>601077</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>中国电信</t>
+          <t>渝农商行</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>rev0</t>
+          <t>np0</t>
         </is>
       </c>
       <c r="F74" t="n">
-        <v>523568920041.49</v>
+        <v>11512747000</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>同 2024 年；取主要会计数据（p7）</t>
+          <t>归母净利润行项目名折行（p199）；按原文补录</t>
         </is>
       </c>
     </row>
@@ -25552,25 +25561,25 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>601800</t>
+          <t>601728</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>中国交建</t>
+          <t>中国电信</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>ta</t>
+          <t>rev</t>
         </is>
       </c>
       <c r="F75" t="n">
-        <v>2019131695690</v>
+        <v>523924731368.75</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>财务报表页无文字层，程序未找到报表；取主要会计数据（p14）；净利润置空</t>
+          <t>同 2024 年；取主要会计数据（p7）</t>
         </is>
       </c>
     </row>
@@ -25582,25 +25591,25 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>601800</t>
+          <t>601728</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>中国交建</t>
+          <t>中国电信</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>ta0</t>
+          <t>rev0</t>
         </is>
       </c>
       <c r="F76" t="n">
-        <v>1858272592553</v>
+        <v>523568920041.49</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>财务报表页无文字层，程序未找到报表；取主要会计数据（p14）；净利润置空</t>
+          <t>同 2024 年；取主要会计数据（p7）</t>
         </is>
       </c>
     </row>
@@ -25622,15 +25631,15 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>rev</t>
+          <t>ta</t>
         </is>
       </c>
       <c r="F77" t="n">
-        <v>731108751343</v>
+        <v>2019131695690</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>财务报表页无文字层，程序未找到报表；取主要会计数据（p14）；净利润置空</t>
+          <t>财务报表页无文字层，程序未找到报表；总资产、营业收入、归母净利润取主要会计数据（p14），净利润取 CSMAR 利润表</t>
         </is>
       </c>
     </row>
@@ -25652,15 +25661,15 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>rev0</t>
+          <t>ta0</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>771944258710</v>
+        <v>1858272592553</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>财务报表页无文字层，程序未找到报表；取主要会计数据（p14）；净利润置空</t>
+          <t>财务报表页无文字层，程序未找到报表；总资产、营业收入、归母净利润取主要会计数据（p14），净利润取 CSMAR 利润表</t>
         </is>
       </c>
     </row>
@@ -25682,15 +25691,15 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>np</t>
+          <t>rev</t>
         </is>
       </c>
       <c r="F79" t="n">
-        <v>14751374779</v>
+        <v>731108751343</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>财务报表页无文字层，程序未找到报表；取主要会计数据（p14）；净利润置空</t>
+          <t>财务报表页无文字层，程序未找到报表；总资产、营业收入、归母净利润取主要会计数据（p14），净利润取 CSMAR 利润表</t>
         </is>
       </c>
     </row>
@@ -25712,15 +25721,135 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
+          <t>rev0</t>
+        </is>
+      </c>
+      <c r="F80" t="n">
+        <v>771944258710</v>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>财务报表页无文字层，程序未找到报表；总资产、营业收入、归母净利润取主要会计数据（p14），净利润取 CSMAR 利润表</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>601800</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>中国交建</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>ni</t>
+        </is>
+      </c>
+      <c r="F81" t="n">
+        <v>20804131324</v>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>财务报表页无文字层，程序未找到报表；总资产、营业收入、归母净利润取主要会计数据（p14），净利润取 CSMAR 利润表</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>601800</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>中国交建</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>ni0</t>
+        </is>
+      </c>
+      <c r="F82" t="n">
+        <v>30346608238</v>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>财务报表页无文字层，程序未找到报表；总资产、营业收入、归母净利润取主要会计数据（p14），净利润取 CSMAR 利润表</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>601800</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>中国交建</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>np</t>
+        </is>
+      </c>
+      <c r="F83" t="n">
+        <v>14751374779</v>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>财务报表页无文字层，程序未找到报表；总资产、营业收入、归母净利润取主要会计数据（p14），净利润取 CSMAR 利润表</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>601800</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>中国交建</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
           <t>np0</t>
         </is>
       </c>
-      <c r="F80" t="n">
+      <c r="F84" t="n">
         <v>23384093178</v>
       </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>财务报表页无文字层，程序未找到报表；取主要会计数据（p14）；净利润置空</t>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>财务报表页无文字层，程序未找到报表；总资产、营业收入、归母净利润取主要会计数据（p14），净利润取 CSMAR 利润表</t>
         </is>
       </c>
     </row>

--- a/年报存档/入表财务效应分析样本.xlsx
+++ b/年报存档/入表财务效应分析样本.xlsx
@@ -6642,13 +6642,13 @@
       </c>
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="n">
-        <v>31366800.6</v>
+        <v>26772194</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>31366800.6</v>
+        <v>26772194</v>
       </c>
       <c r="I63" t="n">
         <v>28006077885.07</v>
@@ -6682,25 +6682,25 @@
         </is>
       </c>
       <c r="T63" t="n">
-        <v>0.1119999763220026</v>
+        <v>0.09559422818813276</v>
       </c>
       <c r="U63" t="n">
-        <v>0.1119999763220026</v>
+        <v>0.09559422818813276</v>
       </c>
       <c r="V63" t="n">
         <v>0.9048940994520798</v>
       </c>
       <c r="W63" t="n">
-        <v>0.2245552583649794</v>
+        <v>0.1916624209568684</v>
       </c>
       <c r="X63" t="n">
-        <v>95032523.06</v>
+        <v>99627129.66</v>
       </c>
       <c r="Y63" t="n">
-        <v>0.6803388410871004</v>
+        <v>0.7132316784952114</v>
       </c>
       <c r="Z63" t="n">
-        <v>24.81563958710189</v>
+        <v>21.18064656106404</v>
       </c>
       <c r="AA63" t="n">
         <v>0</v>

--- a/年报存档/入表财务效应分析样本.xlsx
+++ b/年报存档/入表财务效应分析样本.xlsx
@@ -6642,13 +6642,13 @@
       </c>
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="n">
-        <v>26772194</v>
+        <v>0</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>26772194</v>
+        <v>0</v>
       </c>
       <c r="I63" t="n">
         <v>28006077885.07</v>
@@ -6682,25 +6682,25 @@
         </is>
       </c>
       <c r="T63" t="n">
-        <v>0.09559422818813276</v>
+        <v>0</v>
       </c>
       <c r="U63" t="n">
-        <v>0.09559422818813276</v>
+        <v>0</v>
       </c>
       <c r="V63" t="n">
         <v>0.9048940994520798</v>
       </c>
       <c r="W63" t="n">
-        <v>0.1916624209568684</v>
+        <v>0</v>
       </c>
       <c r="X63" t="n">
-        <v>99627129.66</v>
+        <v>126399323.66</v>
       </c>
       <c r="Y63" t="n">
-        <v>0.7132316784952114</v>
+        <v>0.9048940994520798</v>
       </c>
       <c r="Z63" t="n">
-        <v>21.18064656106404</v>
+        <v>0</v>
       </c>
       <c r="AA63" t="n">
         <v>0</v>

--- a/年报存档/入表财务效应分析样本.xlsx
+++ b/年报存档/入表财务效应分析样本.xlsx
@@ -490,7 +490,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024 年＝期末余额（期初为 0）；2025 年＝期末－期初，即新增资本化减当期摊销的净额</t>
+          <t>当期新增额＝期末－期初，即新增资本化减当期摊销的净额；2024 年绝大多数期初为 0，天威视讯、中远海科、中文在线、海天瑞声 4 家列示了 2024 年以前已资本化的期初余额</t>
         </is>
       </c>
     </row>
@@ -562,7 +562,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>测算入表额÷总资产×100（2024 年与存量口径相同）</t>
+          <t>测算入表额÷总资产×100</t>
         </is>
       </c>
     </row>
@@ -1332,6 +1332,9 @@
       <c r="N7" t="n">
         <v>1834953886</v>
       </c>
+      <c r="O7" t="n">
+        <v>1548231441.85</v>
+      </c>
       <c r="S7" t="inlineStr">
         <is>
           <t>稳健</t>
@@ -1366,7 +1369,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>财务报表页无文字层，程序未找到报表。总资产、营业总收入取 2024 年报「主要会计数据」（p21-22）；净利润、归母净利润取 2025 年报利润表上期数（p151），归母净利润与 2024 年报分季度数据合计一致</t>
+          <t>财务报表页无文字层，程序未找到报表。总资产、营业总收入取 2024 年报「主要会计数据」（p21-22）；净利润、归母净利润取 2025 年报利润表上期数（p151），归母净利润与 2024 年报分季度数据合计一致；上年归母净利润取 CSMAR</t>
         </is>
       </c>
     </row>
@@ -2349,10 +2352,10 @@
         <v>1120013.07</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>596568.7</v>
       </c>
       <c r="H18" t="n">
-        <v>1120013.07</v>
+        <v>523444.3700000001</v>
       </c>
       <c r="I18" t="n">
         <v>4174415166.23</v>
@@ -2392,22 +2395,22 @@
         <v>0.02683041876286366</v>
       </c>
       <c r="U18" t="n">
-        <v>0.02683041876286366</v>
+        <v>0.01253934621152532</v>
       </c>
       <c r="V18" t="n">
         <v>-0.4381697008128806</v>
       </c>
       <c r="W18" t="n">
-        <v>0.08595940269284517</v>
+        <v>0.04017360742775319</v>
       </c>
       <c r="X18" t="n">
-        <v>-6829170.84</v>
+        <v>-6232602.14</v>
       </c>
       <c r="Y18" t="n">
-        <v>-0.5241291035057258</v>
+        <v>-0.4783433082406338</v>
       </c>
       <c r="Z18" t="n">
-        <v>19.61783357757864</v>
+        <v>9.168504201277312</v>
       </c>
       <c r="AA18" t="n">
         <v>0</v>
@@ -2540,10 +2543,10 @@
         <v>8320756.3</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>9253925.23</v>
       </c>
       <c r="H20" t="n">
-        <v>8320756.3</v>
+        <v>-933168.9300000006</v>
       </c>
       <c r="I20" t="n">
         <v>2879902940.65</v>
@@ -2583,22 +2586,22 @@
         <v>0.2889248864103034</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2889248864103034</v>
+        <v>-0.0324027909700798</v>
       </c>
       <c r="V20" t="n">
         <v>7.1930636922477</v>
       </c>
       <c r="W20" t="n">
-        <v>0.4631582121776264</v>
+        <v>-0.05194297701983039</v>
       </c>
       <c r="X20" t="n">
-        <v>120904481.34</v>
+        <v>130158406.57</v>
       </c>
       <c r="Y20" t="n">
-        <v>6.729905480070075</v>
+        <v>7.245006669267531</v>
       </c>
       <c r="Z20" t="n">
-        <v>6.43895608316097</v>
+        <v>-0.7221259152176249</v>
       </c>
       <c r="AA20" t="n">
         <v>0</v>
@@ -3587,10 +3590,10 @@
         <v>7018865.77</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>457455.08</v>
       </c>
       <c r="H31" t="n">
-        <v>7018865.77</v>
+        <v>6561410.689999999</v>
       </c>
       <c r="I31" t="n">
         <v>1634392655.06</v>
@@ -3630,22 +3633,22 @@
         <v>0.4294479510948568</v>
       </c>
       <c r="U31" t="n">
-        <v>0.4294479510948568</v>
+        <v>0.4014586500793547</v>
       </c>
       <c r="V31" t="n">
         <v>-20.93123574981199</v>
       </c>
       <c r="W31" t="n">
-        <v>0.6055344158937344</v>
+        <v>0.5660686669048602</v>
       </c>
       <c r="X31" t="n">
-        <v>-249636841.35</v>
+        <v>-249179386.27</v>
       </c>
       <c r="Y31" t="n">
-        <v>-21.53677016570573</v>
+        <v>-21.49730441671685</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.892970215096706</v>
+        <v>2.704420673824501</v>
       </c>
       <c r="AA31" t="n">
         <v>0</v>
@@ -10199,10 +10202,10 @@
         <v>14129503.48</v>
       </c>
       <c r="G100" t="n">
-        <v>0</v>
+        <v>4342849.45</v>
       </c>
       <c r="H100" t="n">
-        <v>14129503.48</v>
+        <v>9786654.030000001</v>
       </c>
       <c r="I100" t="n">
         <v>808464516.38</v>
@@ -10242,25 +10245,25 @@
         <v>1.747696181307574</v>
       </c>
       <c r="U100" t="n">
-        <v>1.747696181307574</v>
+        <v>1.210523632356922</v>
       </c>
       <c r="V100" t="n">
         <v>4.774905064549566</v>
       </c>
       <c r="W100" t="n">
-        <v>5.959727896099603</v>
+        <v>4.1279437111591</v>
       </c>
       <c r="X100" t="n">
-        <v>-2809013.870000001</v>
+        <v>1533835.579999998</v>
       </c>
       <c r="Y100" t="n">
-        <v>-1.184822831550038</v>
+        <v>0.6469613533904663</v>
       </c>
       <c r="Z100" t="n">
-        <v>124.8135369296982</v>
+        <v>86.45080175114441</v>
       </c>
       <c r="AA100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB100" t="n">
         <v>20.51064734780558</v>
@@ -23311,7 +23314,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G84"/>
+  <dimension ref="A1:G85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23377,7 +23380,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>财务报表页无文字层，程序未找到报表。总资产、营业总收入取 2024 年报「主要会计数据」（p21-22）；净利润、归母净利润取 2025 年报利润表上期数（p151），归母净利润与 2024 年报分季度数据合计一致</t>
+          <t>财务报表页无文字层，程序未找到报表。总资产、营业总收入取 2024 年报「主要会计数据」（p21-22）；净利润、归母净利润取 2025 年报利润表上期数（p151），归母净利润与 2024 年报分季度数据合计一致；上年归母净利润取 CSMAR</t>
         </is>
       </c>
     </row>
@@ -23407,7 +23410,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>财务报表页无文字层，程序未找到报表。总资产、营业总收入取 2024 年报「主要会计数据」（p21-22）；净利润、归母净利润取 2025 年报利润表上期数（p151），归母净利润与 2024 年报分季度数据合计一致</t>
+          <t>财务报表页无文字层，程序未找到报表。总资产、营业总收入取 2024 年报「主要会计数据」（p21-22）；净利润、归母净利润取 2025 年报利润表上期数（p151），归母净利润与 2024 年报分季度数据合计一致；上年归母净利润取 CSMAR</t>
         </is>
       </c>
     </row>
@@ -23437,7 +23440,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>财务报表页无文字层，程序未找到报表。总资产、营业总收入取 2024 年报「主要会计数据」（p21-22）；净利润、归母净利润取 2025 年报利润表上期数（p151），归母净利润与 2024 年报分季度数据合计一致</t>
+          <t>财务报表页无文字层，程序未找到报表。总资产、营业总收入取 2024 年报「主要会计数据」（p21-22）；净利润、归母净利润取 2025 年报利润表上期数（p151），归母净利润与 2024 年报分季度数据合计一致；上年归母净利润取 CSMAR</t>
         </is>
       </c>
     </row>
@@ -23467,7 +23470,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>财务报表页无文字层，程序未找到报表。总资产、营业总收入取 2024 年报「主要会计数据」（p21-22）；净利润、归母净利润取 2025 年报利润表上期数（p151），归母净利润与 2024 年报分季度数据合计一致</t>
+          <t>财务报表页无文字层，程序未找到报表。总资产、营业总收入取 2024 年报「主要会计数据」（p21-22）；净利润、归母净利润取 2025 年报利润表上期数（p151），归母净利润与 2024 年报分季度数据合计一致；上年归母净利润取 CSMAR</t>
         </is>
       </c>
     </row>
@@ -23497,7 +23500,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>财务报表页无文字层，程序未找到报表。总资产、营业总收入取 2024 年报「主要会计数据」（p21-22）；净利润、归母净利润取 2025 年报利润表上期数（p151），归母净利润与 2024 年报分季度数据合计一致</t>
+          <t>财务报表页无文字层，程序未找到报表。总资产、营业总收入取 2024 年报「主要会计数据」（p21-22）；净利润、归母净利润取 2025 年报利润表上期数（p151），归母净利润与 2024 年报分季度数据合计一致；上年归母净利润取 CSMAR</t>
         </is>
       </c>
     </row>
@@ -23527,7 +23530,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>财务报表页无文字层，程序未找到报表。总资产、营业总收入取 2024 年报「主要会计数据」（p21-22）；净利润、归母净利润取 2025 年报利润表上期数（p151），归母净利润与 2024 年报分季度数据合计一致</t>
+          <t>财务报表页无文字层，程序未找到报表。总资产、营业总收入取 2024 年报「主要会计数据」（p21-22）；净利润、归母净利润取 2025 年报利润表上期数（p151），归母净利润与 2024 年报分季度数据合计一致；上年归母净利润取 CSMAR</t>
         </is>
       </c>
     </row>
@@ -23539,25 +23542,25 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>002142</t>
+          <t>000783</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>宁波银行</t>
+          <t>长江证券</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>np</t>
+          <t>np0</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>27127000000</v>
+        <v>1548231441.85</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>利润表「其中：归属于母公司股东 / 的净利润」折成两行（p92）；与主要会计数据（p9）一致</t>
+          <t>财务报表页无文字层，程序未找到报表。总资产、营业总收入取 2024 年报「主要会计数据」（p21-22）；净利润、归母净利润取 2025 年报利润表上期数（p151），归母净利润与 2024 年报分季度数据合计一致；上年归母净利润取 CSMAR</t>
         </is>
       </c>
     </row>
@@ -23579,11 +23582,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>np0</t>
+          <t>np</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>25535000000</v>
+        <v>27127000000</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -23599,25 +23602,25 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>600050</t>
+          <t>002142</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>中国联通</t>
+          <t>宁波银行</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>rev</t>
+          <t>np0</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>389589219642</v>
+        <v>25535000000</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>利润表页混入目录文字，营业收入行无法识别（p80）；取主要会计数据（p7）</t>
+          <t>利润表「其中：归属于母公司股东 / 的净利润」折成两行（p92）；与主要会计数据（p9）一致</t>
         </is>
       </c>
     </row>
@@ -23639,11 +23642,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>rev0</t>
+          <t>rev</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>372596794135</v>
+        <v>389589219642</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -23659,25 +23662,25 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>600704</t>
+          <t>600050</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>物产中大</t>
+          <t>中国联通</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>np</t>
+          <t>rev0</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3079003701.43</v>
+        <v>372596794135</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>归母净利润行项目名折行（p170）；按诊断页原文行补录</t>
+          <t>利润表页混入目录文字，营业收入行无法识别（p80）；取主要会计数据（p7）</t>
         </is>
       </c>
     </row>
@@ -23699,11 +23702,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>np0</t>
+          <t>np</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3617056493.41</v>
+        <v>3079003701.43</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -23719,25 +23722,25 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>600810</t>
+          <t>600704</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>神马股份</t>
+          <t>物产中大</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>ta</t>
+          <t>np0</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>28006077885.07</v>
+        <v>3617056493.41</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>报表金额与项目名上下错位一行（p143-153）。总资产、归母净利润取主要会计数据（p9，上期为调整后数）；净利润取 CSMAR 利润表；上年净利润经追溯调整、无法确定，置空；研发费用无法确定，置空</t>
+          <t>归母净利润行项目名折行（p170）；按诊断页原文行补录</t>
         </is>
       </c>
     </row>
@@ -23759,11 +23762,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>ta0</t>
+          <t>ta</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>32085531546.09</v>
+        <v>28006077885.07</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -23789,11 +23792,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>ni</t>
+          <t>ta0</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>126399323.66</v>
+        <v>32085531546.09</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -23819,8 +23822,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>ni0</t>
-        </is>
+          <t>ni</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>126399323.66</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -23846,11 +23852,8 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>np</t>
-        </is>
-      </c>
-      <c r="F18" t="n">
-        <v>33529751.5</v>
+          <t>ni0</t>
+        </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -23876,11 +23879,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>np0</t>
+          <t>np</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>149456379.11</v>
+        <v>33529751.5</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -23906,11 +23909,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>rd</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>315603443.12</v>
+          <t>np0</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>149456379.11</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -23926,25 +23929,25 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>600941</t>
+          <t>600810</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>中国移动</t>
+          <t>神马股份</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>ta</t>
-        </is>
-      </c>
-      <c r="F21" t="n">
-        <v>2072827000000</v>
+          <t>rd</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>315603443.12</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>资产总计行金额排在下一行（p94）；取主要会计数据（p8）</t>
+          <t>报表金额与项目名上下错位一行（p143-153）。总资产、归母净利润取主要会计数据（p9，上期为调整后数）；净利润取 CSMAR 利润表；上年净利润经追溯调整、无法确定，置空；研发费用无法确定，置空</t>
         </is>
       </c>
     </row>
@@ -23966,11 +23969,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>ta0</t>
+          <t>ta</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1957357000000</v>
+        <v>2072827000000</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -23986,25 +23989,25 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>600998</t>
+          <t>600941</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>九州通</t>
+          <t>中国移动</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>np</t>
+          <t>ta0</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2507391943.72</v>
+        <v>1957357000000</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>归母净利润行项目名折行（p167）；与 2025 年报上期数一致</t>
+          <t>资产总计行金额排在下一行（p94）；取主要会计数据（p8）</t>
         </is>
       </c>
     </row>
@@ -24026,11 +24029,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>np0</t>
+          <t>np</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2174042838.43</v>
+        <v>2507391943.72</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -24046,25 +24049,25 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>601066</t>
+          <t>600998</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>中信建投</t>
+          <t>九州通</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>np</t>
+          <t>np0</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>7223221368.58</v>
+        <v>2174042838.43</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>项目名前有「-」号（p175）；与 2025 年报上期数一致</t>
+          <t>归母净利润行项目名折行（p167）；与 2025 年报上期数一致</t>
         </is>
       </c>
     </row>
@@ -24086,11 +24089,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>np0</t>
+          <t>np</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>7034486447.93</v>
+        <v>7223221368.58</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -24106,25 +24109,25 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>601728</t>
+          <t>601066</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>中国电信</t>
+          <t>中信建投</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>rev</t>
+          <t>np0</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>523568920041.49</v>
+        <v>7034486447.93</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>附注编号「五(39)/十六(5)」未识别（p90）；与主要会计数据一致</t>
+          <t>项目名前有「-」号（p175）；与 2025 年报上期数一致</t>
         </is>
       </c>
     </row>
@@ -24146,11 +24149,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>rev0</t>
+          <t>rev</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>507842674997.4</v>
+        <v>523568920041.49</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -24166,28 +24169,25 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>601800</t>
+          <t>601728</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>中国交建</t>
+          <t>中国电信</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>ta</t>
-        </is>
-      </c>
-      <c r="E29" t="n">
-        <v>149591842</v>
+          <t>rev0</t>
+        </is>
       </c>
       <c r="F29" t="n">
-        <v>1858272592553</v>
+        <v>507842674997.4</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>程序误取追溯调整表（p219），作废。总资产、营业收入、归母净利润取主要会计数据（p13，上期为调整后数）；净利润取 CSMAR 利润表，上年净利润取 p219 追溯调整表的调整后数</t>
+          <t>附注编号「五(39)/十六(5)」未识别（p90）；与主要会计数据一致</t>
         </is>
       </c>
     </row>
@@ -24209,14 +24209,14 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>ta0</t>
+          <t>ta</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1684412378006</v>
+        <v>149591842</v>
       </c>
       <c r="F30" t="n">
-        <v>1684412378006</v>
+        <v>1858272592553</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -24242,11 +24242,14 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>rev</t>
-        </is>
+          <t>ta0</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>1684412378006</v>
       </c>
       <c r="F31" t="n">
-        <v>771944258710</v>
+        <v>1684412378006</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -24272,11 +24275,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>rev0</t>
+          <t>rev</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>758718749687</v>
+        <v>771944258710</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -24302,14 +24305,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>ni</t>
-        </is>
-      </c>
-      <c r="E33" t="n">
-        <v>30224114836</v>
+          <t>rev0</t>
+        </is>
       </c>
       <c r="F33" t="n">
-        <v>30346608238</v>
+        <v>758718749687</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -24335,14 +24335,14 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>ni0</t>
+          <t>ni</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>12048019</v>
+        <v>30224114836</v>
       </c>
       <c r="F34" t="n">
-        <v>30236162855</v>
+        <v>30346608238</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -24368,11 +24368,14 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>np</t>
-        </is>
+          <t>ni0</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>12048019</v>
       </c>
       <c r="F35" t="n">
-        <v>23384093178</v>
+        <v>30236162855</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -24398,11 +24401,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>np0</t>
+          <t>np</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>23816263046</v>
+        <v>23384093178</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -24418,25 +24421,25 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>601929</t>
+          <t>601800</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>吉视传媒</t>
+          <t>中国交建</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>ta</t>
+          <t>np0</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>13072785903.05</v>
+        <v>23816263046</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>资产总计行金额错位（p92）；取 2025 年报主要会计数据中的 2024、2023 年末数</t>
+          <t>程序误取追溯调整表（p219），作废。总资产、营业收入、归母净利润取主要会计数据（p13，上期为调整后数）；净利润取 CSMAR 利润表，上年净利润取 p219 追溯调整表的调整后数</t>
         </is>
       </c>
     </row>
@@ -24458,11 +24461,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>ta0</t>
+          <t>ta</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>14614480558.19</v>
+        <v>13072785903.05</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -24478,25 +24481,25 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>603698</t>
+          <t>601929</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>航天工程</t>
+          <t>吉视传媒</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>np</t>
+          <t>ta0</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>189206363.11</v>
+        <v>14614480558.19</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>归母净利润行项目名折行（p76）；与 2025 年报上期数一致</t>
+          <t>资产总计行金额错位（p92）；取 2025 年报主要会计数据中的 2024、2023 年末数</t>
         </is>
       </c>
     </row>
@@ -24518,11 +24521,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>np0</t>
+          <t>np</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>187158325.77</v>
+        <v>189206363.11</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -24538,25 +24541,25 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>605006</t>
+          <t>603698</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>山东玻纤</t>
+          <t>航天工程</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>ta</t>
+          <t>np0</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>7138031412.86</v>
+        <v>187158325.77</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>报表金额与项目名错位（p118、p124）；总资产取主要会计数据（p7），净利润取持续经营净利润行，与 2025 年报上期数一致</t>
+          <t>归母净利润行项目名折行（p76）；与 2025 年报上期数一致</t>
         </is>
       </c>
     </row>
@@ -24578,11 +24581,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>ta0</t>
+          <t>ta</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>6647208749.67</v>
+        <v>7138031412.86</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -24608,11 +24611,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>ni</t>
+          <t>ta0</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>-98930537.59999999</v>
+        <v>6647208749.67</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -24638,11 +24641,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>ni0</t>
+          <t>ni</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>105339606.41</v>
+        <v>-98930537.59999999</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -24668,14 +24671,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>np</t>
-        </is>
-      </c>
-      <c r="E45" t="n">
-        <v>-98930537.59999999</v>
+          <t>ni0</t>
+        </is>
       </c>
       <c r="F45" t="n">
-        <v>-98930537.59999999</v>
+        <v>105339606.41</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -24701,11 +24701,14 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>np0</t>
-        </is>
+          <t>np</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>-98930537.59999999</v>
       </c>
       <c r="F46" t="n">
-        <v>105339606.41</v>
+        <v>-98930537.59999999</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -24721,25 +24724,25 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>688066</t>
+          <t>605006</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>航天宏图</t>
+          <t>山东玻纤</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>np</t>
+          <t>np0</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>-1392889049.16</v>
+        <v>105339606.41</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>归母净利润行项目名折行（p142）；与 2025 年报上期数一致</t>
+          <t>报表金额与项目名错位（p118、p124）；总资产取主要会计数据（p7），净利润取持续经营净利润行，与 2025 年报上期数一致</t>
         </is>
       </c>
     </row>
@@ -24761,11 +24764,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>np0</t>
+          <t>np</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>-374205669.01</v>
+        <v>-1392889049.16</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -24781,25 +24784,25 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>688676</t>
+          <t>688066</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>金盘科技</t>
+          <t>航天宏图</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>np</t>
+          <t>np0</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>574421452.41</v>
+        <v>-374205669.01</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>归母净利润行项目名折行（p189）；与 2025 年报上期数一致</t>
+          <t>归母净利润行项目名折行（p142）；与 2025 年报上期数一致</t>
         </is>
       </c>
     </row>
@@ -24821,11 +24824,11 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>np0</t>
+          <t>np</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>504660243.92</v>
+        <v>574421452.41</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -24836,30 +24839,30 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>002142</t>
+          <t>688676</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>宁波银行</t>
+          <t>金盘科技</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>np</t>
+          <t>np0</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>29333000000</v>
+        <v>504660243.92</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>同 2024 年（p86）；与主要会计数据（p9）一致</t>
+          <t>归母净利润行项目名折行（p189）；与 2025 年报上期数一致</t>
         </is>
       </c>
     </row>
@@ -24881,11 +24884,11 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>np0</t>
+          <t>np</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>27127000000</v>
+        <v>29333000000</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -24901,25 +24904,25 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>002673</t>
+          <t>002142</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>西部证券</t>
+          <t>宁波银行</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>ta</t>
+          <t>np0</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>121660733218.23</v>
+        <v>27127000000</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>财务报表页无文字层，程序未找到报表；总资产、营业收入、归母净利润取主要会计数据（p20），净利润取 CSMAR 利润表</t>
+          <t>同 2024 年（p86）；与主要会计数据（p9）一致</t>
         </is>
       </c>
     </row>
@@ -24941,11 +24944,11 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>ta0</t>
+          <t>ta</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>95964078079.73</v>
+        <v>121660733218.23</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -24971,11 +24974,11 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>rev</t>
+          <t>ta0</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>5984624114.13</v>
+        <v>95964078079.73</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -25001,11 +25004,11 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>rev0</t>
+          <t>rev</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>6712047091.34</v>
+        <v>5984624114.13</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -25031,11 +25034,11 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>ni</t>
+          <t>rev0</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>1812955974.25</v>
+        <v>6712047091.34</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -25061,11 +25064,11 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>ni0</t>
+          <t>ni</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>1428086862.83</v>
+        <v>1812955974.25</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -25091,11 +25094,11 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>np</t>
+          <t>ni0</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>1753652721</v>
+        <v>1428086862.83</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -25121,11 +25124,11 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>np0</t>
+          <t>np</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>1403260839.02</v>
+        <v>1753652721</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -25141,25 +25144,25 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>600029</t>
+          <t>002673</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>南方航空</t>
+          <t>西部证券</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>np</t>
+          <t>np0</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>857000000</v>
+        <v>1403260839.02</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>项目名为「归属于母公司股东的净利润/(亏损)」（p98）；按原文补录</t>
+          <t>财务报表页无文字层，程序未找到报表；总资产、营业收入、归母净利润取主要会计数据（p20），净利润取 CSMAR 利润表</t>
         </is>
       </c>
     </row>
@@ -25181,11 +25184,11 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>np0</t>
+          <t>np</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>-1696000000</v>
+        <v>857000000</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -25201,25 +25204,25 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>600030</t>
+          <t>600029</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>中信证券</t>
+          <t>南方航空</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>np</t>
+          <t>np0</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>30076100951.5</v>
+        <v>-1696000000</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>归母净利润行项目名折行（p183）；按原文补录</t>
+          <t>项目名为「归属于母公司股东的净利润/(亏损)」（p98）；按原文补录</t>
         </is>
       </c>
     </row>
@@ -25241,11 +25244,11 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>np0</t>
+          <t>np</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>21703696593.02</v>
+        <v>30076100951.5</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -25261,25 +25264,25 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>600050</t>
+          <t>600030</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>中国联通</t>
+          <t>中信证券</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>rev</t>
+          <t>np0</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>392222880560</v>
+        <v>21703696593.02</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>同 2024 年；取主要会计数据（p7）</t>
+          <t>归母净利润行项目名折行（p183）；按原文补录</t>
         </is>
       </c>
     </row>
@@ -25301,11 +25304,11 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>rev0</t>
+          <t>rev</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>389589219642</v>
+        <v>392222880560</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -25321,25 +25324,25 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>600600</t>
+          <t>600050</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>青岛啤酒</t>
+          <t>中国联通</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>rev</t>
+          <t>rev0</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>32473493664</v>
+        <v>389589219642</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>利润表营业收入行未识别（p72）；取主要会计数据（p5）</t>
+          <t>同 2024 年；取主要会计数据（p7）</t>
         </is>
       </c>
     </row>
@@ -25361,11 +25364,11 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>rev0</t>
+          <t>rev</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>32137830111</v>
+        <v>32473493664</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -25381,25 +25384,25 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>600926</t>
+          <t>600600</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>杭州银行</t>
+          <t>青岛啤酒</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>np</t>
+          <t>rev0</t>
         </is>
       </c>
       <c r="F69" t="n">
-        <v>19029250000</v>
+        <v>32137830111</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>归母净利润行项目名折行（p118）；按原文补录</t>
+          <t>利润表营业收入行未识别（p72）；取主要会计数据（p5）</t>
         </is>
       </c>
     </row>
@@ -25421,11 +25424,11 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>np0</t>
+          <t>np</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>16982563000</v>
+        <v>19029250000</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -25441,25 +25444,25 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>601066</t>
+          <t>600926</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>中信建投</t>
+          <t>杭州银行</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>np</t>
+          <t>np0</t>
         </is>
       </c>
       <c r="F71" t="n">
-        <v>9439423821.459999</v>
+        <v>16982563000</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>项目名前有「-」号（p170）；按原文补录</t>
+          <t>归母净利润行项目名折行（p118）；按原文补录</t>
         </is>
       </c>
     </row>
@@ -25481,11 +25484,11 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>np0</t>
+          <t>np</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>7223221368.58</v>
+        <v>9439423821.459999</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -25501,25 +25504,25 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>601066</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>渝农商行</t>
+          <t>中信建投</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>np</t>
+          <t>np0</t>
         </is>
       </c>
       <c r="F73" t="n">
-        <v>12128421000</v>
+        <v>7223221368.58</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>归母净利润行项目名折行（p199）；按原文补录</t>
+          <t>项目名前有「-」号（p170）；按原文补录</t>
         </is>
       </c>
     </row>
@@ -25541,11 +25544,11 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>np0</t>
+          <t>np</t>
         </is>
       </c>
       <c r="F74" t="n">
-        <v>11512747000</v>
+        <v>12128421000</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -25561,25 +25564,25 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>601728</t>
+          <t>601077</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>中国电信</t>
+          <t>渝农商行</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>rev</t>
+          <t>np0</t>
         </is>
       </c>
       <c r="F75" t="n">
-        <v>523924731368.75</v>
+        <v>11512747000</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>同 2024 年；取主要会计数据（p7）</t>
+          <t>归母净利润行项目名折行（p199）；按原文补录</t>
         </is>
       </c>
     </row>
@@ -25601,11 +25604,11 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>rev0</t>
+          <t>rev</t>
         </is>
       </c>
       <c r="F76" t="n">
-        <v>523568920041.49</v>
+        <v>523924731368.75</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -25621,25 +25624,25 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>601800</t>
+          <t>601728</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>中国交建</t>
+          <t>中国电信</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>ta</t>
+          <t>rev0</t>
         </is>
       </c>
       <c r="F77" t="n">
-        <v>2019131695690</v>
+        <v>523568920041.49</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>财务报表页无文字层，程序未找到报表；总资产、营业收入、归母净利润取主要会计数据（p14），净利润取 CSMAR 利润表</t>
+          <t>同 2024 年；取主要会计数据（p7）</t>
         </is>
       </c>
     </row>
@@ -25661,11 +25664,11 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>ta0</t>
+          <t>ta</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>1858272592553</v>
+        <v>2019131695690</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -25691,11 +25694,11 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>rev</t>
+          <t>ta0</t>
         </is>
       </c>
       <c r="F79" t="n">
-        <v>731108751343</v>
+        <v>1858272592553</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
@@ -25721,11 +25724,11 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>rev0</t>
+          <t>rev</t>
         </is>
       </c>
       <c r="F80" t="n">
-        <v>771944258710</v>
+        <v>731108751343</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -25751,11 +25754,11 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>ni</t>
+          <t>rev0</t>
         </is>
       </c>
       <c r="F81" t="n">
-        <v>20804131324</v>
+        <v>771944258710</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -25781,11 +25784,11 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>ni0</t>
+          <t>ni</t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>30346608238</v>
+        <v>20804131324</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -25811,11 +25814,11 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>np</t>
+          <t>ni0</t>
         </is>
       </c>
       <c r="F83" t="n">
-        <v>14751374779</v>
+        <v>30346608238</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -25841,13 +25844,43 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
+          <t>np</t>
+        </is>
+      </c>
+      <c r="F84" t="n">
+        <v>14751374779</v>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>财务报表页无文字层，程序未找到报表；总资产、营业收入、归母净利润取主要会计数据（p14），净利润取 CSMAR 利润表</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>601800</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>中国交建</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
           <t>np0</t>
         </is>
       </c>
-      <c r="F84" t="n">
+      <c r="F85" t="n">
         <v>23384093178</v>
       </c>
-      <c r="G84" t="inlineStr">
+      <c r="G85" t="inlineStr">
         <is>
           <t>财务报表页无文字层，程序未找到报表；总资产、营业收入、归母净利润取主要会计数据（p14），净利润取 CSMAR 利润表</t>
         </is>

--- a/年报存档/入表财务效应分析样本.xlsx
+++ b/年报存档/入表财务效应分析样本.xlsx
@@ -586,7 +586,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>测算入表额÷营业收入×100，即若全部费用化净利率下降的百分点</t>
+          <t>税前利润率影响：测算入表额÷营业收入×100，即若全部费用化税前利润率下降的百分点；未扣除所得税影响，税后口径见 csmar/tests_v6.py 第 5 部分</t>
         </is>
       </c>
     </row>
@@ -598,7 +598,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>净利润－测算入表额；及其÷营业收入</t>
+          <t>净利润－测算入表额；及其÷营业收入（未扣除所得税影响）</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>全部费用化后净利润符号改变取 1</t>
+          <t>全部费用化后净利润符号改变取 1（按未扣除所得税影响的入表额判断）</t>
         </is>
       </c>
     </row>

--- a/年报存档/入表财务效应分析样本.xlsx
+++ b/年报存档/入表财务效应分析样本.xlsx
@@ -478,7 +478,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>数据资源（存货、无形资产、开发支出项下合计）期末、期初余额，元；取自数据资源提取结果.xlsx「汇总」页</t>
+          <t>数据资源（存货、无形资产、开发支出项下合计）期末、期初余额，元；取自数据资源提取结果.xlsx「汇总」页；神马股份 2024、金圆股份 2025、信达证券 2025 经核对实际未列报数据资源，记为 0，分析中不计入入表企业</t>
         </is>
       </c>
     </row>
